--- a/artfynd/A 50213-2023 artfynd.xlsx
+++ b/artfynd/A 50213-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124193067</v>
+        <v>124192715</v>
       </c>
       <c r="B2" t="n">
         <v>57666</v>
@@ -709,24 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595142</v>
+        <v>595070</v>
       </c>
       <c r="R2" t="n">
-        <v>6928413</v>
+        <v>6928419</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124192715</v>
+        <v>124193067</v>
       </c>
       <c r="B3" t="n">
         <v>57666</v>
@@ -819,21 +816,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595070</v>
+        <v>595142</v>
       </c>
       <c r="R3" t="n">
-        <v>6928419</v>
+        <v>6928413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 50213-2023 artfynd.xlsx
+++ b/artfynd/A 50213-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124192715</v>
+        <v>124193067</v>
       </c>
       <c r="B2" t="n">
         <v>57666</v>
@@ -709,21 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Talltita, Mpd</t>
+          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595070</v>
+        <v>595142</v>
       </c>
       <c r="R2" t="n">
-        <v>6928419</v>
+        <v>6928413</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124193067</v>
+        <v>124192715</v>
       </c>
       <c r="B3" t="n">
         <v>57666</v>
@@ -816,24 +819,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Talltita, Näsvattnet, Sättna, Mpd</t>
+          <t>Talltita, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595142</v>
+        <v>595070</v>
       </c>
       <c r="R3" t="n">
-        <v>6928413</v>
+        <v>6928419</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
